--- a/www/download/COUNTRY.AUS.EXI382.xlsx
+++ b/www/download/COUNTRY.AUS.EXI382.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Austrália</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -967,2643 +972,4879 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1095</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1095</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1095</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1095</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1095</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1095</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1095</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1095</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1095</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1095</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1095</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1095</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1095</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1095</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1095</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1095</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1095</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1095</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1095</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1095</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1095</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1095</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1095</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1095</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1095</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1095</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.1095</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>10.572</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>7.763</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>8.323</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>8.39</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>8.571</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>8.72</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>8.948</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>9.081</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>9.245</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>9.465</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>9.623</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>9.969</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>10.218</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>10.512</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>10.74</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>10.921</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>11.215</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>11.395</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>11.546</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>10.416</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>9.643</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>9.819</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>9.987</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>10.297</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>9.799</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>9.614</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>9.634</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>9.298</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>6.498</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>7.063</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>7.12</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>7.32</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>7.456</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>7.688</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>7.833</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>7.964</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>8.196</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>8.355</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>8.678</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>8.944</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>9.252</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>9.472</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>9.629</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>9.889</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>10.072</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>10.213</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>9.209</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>8.502</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>8.655</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>8.77</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>9.037</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>8.621</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>8.468</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>8.483</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>19097.64</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>14507.826</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>15448.211</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>15558.233</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>15815.484</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>16001.517</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>16349.601</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>16445.736</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>16719.945</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>17008.748</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>17336.604</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>17904.524</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>18312.139</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>18844.801</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>19188.989</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>19242.531</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>19878.819</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>20057.919</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>20161.636</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>18217.121</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>16871.245</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>17130.323</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>17634.785</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>18370.706</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>17494.803</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>17205.919</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>17256.738</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>16754.465</t>
+          <t>44747315254.099</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>9597.736</t>
+          <t>27834137396.5421</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>10602.33</t>
+          <t>26519583211.7165</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>10614.764</t>
+          <t>28904428973.6676</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>11006.706</t>
+          <t>33554136795.1571</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>11165.384</t>
+          <t>33834486436.2994</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>11538.466</t>
+          <t>35751345797.3948</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>11708.711</t>
+          <t>40794175258.5003</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>11880.586</t>
+          <t>38327064088.2249</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>12263.125</t>
+          <t>45558590197.2949</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>12592.446</t>
+          <t>48321819426.0623</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>13099.361</t>
+          <t>45242875312.684</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>13550.895</t>
+          <t>41463510778.5874</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>14127.637</t>
+          <t>47150768293.0445</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>14445.014</t>
+          <t>48905819532.3807</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>14471.033</t>
+          <t>44522628125.7205</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>14990.991</t>
+          <t>50575890649.5773</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>15210.466</t>
+          <t>47823470575.4806</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>15346.896</t>
+          <t>47625646517.1512</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>16011.084</t>
+          <t>39907898422.3586</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>14779.538</t>
+          <t>34492180464.8117</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>15007.815</t>
+          <t>32783406322.0713</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>15410.976</t>
+          <t>33647634132.9447</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16061.608</t>
+          <t>35344803447.0357</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>15341.586</t>
+          <t>32300380801.4458</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15113.767</t>
+          <t>33818780716.5576</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>15151.871</t>
+          <t>34763908841.3031</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>12633720243.8769</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>9613356583.54228</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>12627556598.6393</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>10712157892.922</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>15895166526.8692</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>12919261120.4873</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>12891277695.2379</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>12872819301.1214</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>12955096134.8369</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>17545418211.2407</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>17215402698.7601</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>17372619309.4471</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>14584988433.6887</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>15872360179.2415</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>16098575265.1342</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>17503197529.9514</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>18411846814.5864</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>17901595957.0092</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>18747389205.9725</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>14391079871.0613</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>11610088681.7831</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>14812192589.9043</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>14957264427.7096</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14927929018.3627</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>14010835050.919</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14909136661.2436</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>14621425123.2015</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>15485278.2377639</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>8194295.41191192</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>6692849.55933642</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>8408384.32010137</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>8122275.59225796</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>7196493.53776237</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>7313235.0478051</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>7731411.48180802</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>7481103.76899376</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>6995754.86063787</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>6613472.11574807</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>6035181.15127631</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>4795387.63615969</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>5427736.0027874</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>5907534.99041684</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>4128499.8076394</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>4044001.52477413</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>3444611.30996743</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>3684041.33416152</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>4101495.55510177</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>3077090.58070199</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>2883245.62184296</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2956657.31048871</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>3217680.55917382</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2955633.67089472</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>3036193.51867595</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>2982262.6596701</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>37624.6283836973</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>60606.6112523945</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>66601.3052730638</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>69148.7584540321</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>73833.1936288925</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>88253.1701324743</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>91339.302806033</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>88768.3102422624</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>82085.5302223597</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>81227.7761305026</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>89413.0303499825</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>97802.0066122459</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>104445.5915207</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>107928.195665432</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>111667.066949177</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>130743.36350925</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>140172.011822235</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>156177.529552788</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>155346.413333335</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>144488.611668759</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>153192.24695431</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>139151.504251506</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>152157.079444895</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>155525.998352766</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>158950.320184371</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>146391.018565807</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>145608.56965307</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>166800.210542846</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>211513.626092526</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>219492.619379992</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>245946.081379178</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>301158.271056238</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>363003.893811456</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>385140.363424</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>425998.75209484</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>367663.153299373</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>427085.440598152</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>485623.257061724</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>486374.930441717</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>461816.940453793</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>527688.272636003</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>548486.058018378</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>575827.165940957</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>680969.509138428</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>710721.292143832</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>691380.522201665</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>599665.613215486</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>585475.346351323</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>507206.430814732</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>550377.401634763</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>562281.204379765</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>547487.279319838</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>545309.476108965</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>550335.626740787</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>0.326170304643834</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>-0.00162486259661354</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>-0.160381475452005</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-0.00909193590124657</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-0.307543815826258</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-0.135756739037145</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-0.104940093130389</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-0.0904315328205323</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>-0.082941147147905</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-0.301063957988933</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>-0.268536085949019</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>-0.245976622945119</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>-0.0709012337160024</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>-0.109922123713151</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>-0.102714728346944</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>-0.173234880355795</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>-0.18579644774559</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>-0.150329056888365</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>-0.1813848813089</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0.112570003852088</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>0.272990922842639</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>0.0132068614941929</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>0.0303338853243189</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>0.075943499184062</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>0.0949801089242677</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>0.0137251687855806</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>0.0362786488657223</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1358.72632082532</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1479.31931731052</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1787.94729966893</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1504.57995321728</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2171.55983535699</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>1732.7799995292</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1676.84873373865</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1643.47151060615</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>1626.60507688352</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2140.86000991218</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2060.58969894005</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2001.89203966848</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>1630.79202031516</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>1715.5784411033</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>1699.5962062005</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>1817.79635364235</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>1861.7759231686</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1777.30964695323</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>1835.6038465882</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>1562.76502457379</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>1365.55583793685</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>1711.38392196855</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>1705.41472066372</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>1651.85253265626</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>1625.15263878436</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>1760.73147435425</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>1723.69029778616</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>28875736106.4401</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>10978688279.8708</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>11805173532.3055</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>11393804699.9997</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>15579868590.4663</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>16797157224.9723</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>17877084918.9298</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.245</t>
+          <t>18868770892.3302</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.259</t>
+          <t>18494042280.7974</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.282</t>
+          <t>25379083003.1</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.316</t>
+          <t>29536204488.9428</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.338</t>
+          <t>28468840535.4298</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.366</t>
+          <t>23079576686.151</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.363</t>
+          <t>30801132809.5118</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>29915973251.5318</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.482</t>
+          <t>34730699949.8759</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.546</t>
+          <t>35818633211.1839</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.591</t>
+          <t>33922412166.5065</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.565</t>
+          <t>36300788282.8445</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.548</t>
+          <t>29211016061.5199</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0.557</t>
+          <t>26141857792.5906</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>0.579</t>
+          <t>32037406200.4392</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>0.611</t>
+          <t>32305951787.1158</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0.597</t>
+          <t>31343228095.6549</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.595</t>
+          <t>28959457985.4558</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>32298173829.5407</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>0.622</t>
+          <t>32415596926.8871</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>31913607815.1709</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>11464107821.8862</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>12559421663.7237</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>12277852772.8155</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>16286733343.4682</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>15721738465.5141</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>16912474452.2809</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>18129068893.1543</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>17586887843.0853</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>24333815335.7981</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>28152754715.3016</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>27125173369.7595</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>21824979527.7787</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>29181261743.5336</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>28588383802.0494</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>33191453916.7226</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>34633034807.9774</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>32889544004.6296</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>34662103546.204</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>28015052068.7686</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>24824863505.7466</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>29657936260.1457</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>32735889698.2662</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>31552933037.4787</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>28967710706.9859</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>32587011725.0971</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>31198382232.1307</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>-3037871708.73082</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>-485419542.015404</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>-754248131.41825</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-884048072.815776</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-706864753.001902</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>1075418759.45822</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>964610466.648905</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>739701999.17588</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>907154437.712036</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>1045267667.3019</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>1383449773.64122</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>1343667165.6703</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>1254597158.37235</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>1619871065.97822</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>1327589449.48238</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>1539246033.15334</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>1185598403.2065</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>1032868161.87692</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>1638684736.6405</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>1195963992.75124</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>1316994286.84405</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>2379469940.29347</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>-429937911.150389</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>-209704941.823857</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>-8252721.53004325</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>-288837895.556419</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>1217214694.75637</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.579</t>
+          <t>1801.90249881651</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.663</t>
+          <t>1476.91562668337</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.749</t>
+          <t>1501.1936737176</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.664</t>
+          <t>1490.90040872433</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.782</t>
+          <t>1503.71003729626</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.875</t>
+          <t>1497.54343732433</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.847</t>
+          <t>1500.88007145454</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.898</t>
+          <t>1494.84986275516</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.948</t>
+          <t>1491.69258585019</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1.058</t>
+          <t>1496.32422182779</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1507.24700643982</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>1.265</t>
+          <t>1509.47339625011</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>1.379</t>
+          <t>1515.1668541406</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>1.385</t>
+          <t>1526.99841546073</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1.397</t>
+          <t>1525.02264358112</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1.855</t>
+          <t>1502.89061980792</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>2.103</t>
+          <t>1515.86457014561</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2.329</t>
+          <t>1510.12836392816</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>1502.65306074464</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2.067</t>
+          <t>1738.68548940997</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>2.117</t>
+          <t>1738.34018632839</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>2.225</t>
+          <t>1733.98593238937</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2.365</t>
+          <t>1757.14657523074</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>2.324</t>
+          <t>1777.29999412223</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2.311</t>
+          <t>1779.50981343466</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2.332</t>
+          <t>1784.89781102585</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2.434</t>
+          <t>1786.2234528528</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>1806.38986923122</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>1868.72239582695</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>1856.10922635139</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>1854.31189349544</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>1845.21057507172</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>1835.12058810061</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.239</t>
+          <t>1827.15900507695</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.245</t>
+          <t>1810.98499080549</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.259</t>
+          <t>1808.44138229476</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.282</t>
+          <t>1796.9961352748</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.316</t>
+          <t>1801.52385148616</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.338</t>
+          <t>1796.11015097539</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.366</t>
+          <t>1792.09247330813</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.363</t>
+          <t>1792.66005593527</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>1786.63436216813</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.482</t>
+          <t>1762.03975605807</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.546</t>
+          <t>1772.58390669269</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.591</t>
+          <t>1760.30044406966</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.565</t>
+          <t>1746.26139135249</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.548</t>
+          <t>1748.93746070352</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>0.557</t>
+          <t>1749.52603948594</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>0.579</t>
+          <t>1744.62908781226</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>0.611</t>
+          <t>1765.85037658168</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>0.597</t>
+          <t>1784.144438897</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>0.595</t>
+          <t>1785.39828115579</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>1789.67451472114</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>0.622</t>
+          <t>1791.18362344698</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>70554.304448319</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>81564.8336208579</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>94145.5358992821</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>78217.350207212</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>96786.9374302227</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>122878.245666371</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>113332.129197209</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>108806.7420003</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>104536.275158046</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>122219.648272623</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>150310.039684829</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>160127.920034379</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>174879.537864979</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>200309.041812239</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>174622.659289114</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>256042.454548101</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>296969.168595666</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>303544.85625454</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>298451.020352435</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>266295.568156683</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>267581.845229033</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>312002.810026438</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>342035.555142307</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>373408.532292286</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>369334.995583662</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>377222.083627386</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>387275.084159547</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>6686214965.32631</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>4595857689.44191</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>4320940158.63295</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>4397925563.68057</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>5386615402.03959</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>5529776345.01563</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>5518531905.50896</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>6127130374.5504</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>5106221084.88358</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>5981813003.96671</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>6597692271.41557</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>6056160121.05181</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>5235624189.3659</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>6710978340.68965</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>6099800801.86909</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>5982443182.8647</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>7184975205.50549</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>5971429580.96413</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>6291050009.20149</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>5957070986.44582</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>4767329031.32537</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>4708133956.42518</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>5703440050.80466</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>6499398873.99427</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>5711780404.19582</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>6138149105.57123</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>5794884181.28786</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>72329.6510935192</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>80334.6310145671</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>98572.2263973384</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>89338.949723572</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>108093.01983649</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>122379.037534994</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>113378.207320541</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>121483.665093078</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>122061.652214678</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>141770.888634751</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>164841.55198075</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>174142.961373877</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>198826.60072466</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>198318.832588099</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>184421.720533979</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>243655.926394191</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>300583.5156422</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>324534.241545817</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>304949.646108562</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>288279.147222584</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>301051.411273344</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>302825.824159565</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>335782.996962506</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>332827.107042874</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>307229.139667154</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>313260.152801419</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>321383.235910962</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>19097.64</t>
+          <t>36567731530.8328</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>14507.826</t>
+          <t>15324645012.2213</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>15448.211</t>
+          <t>16954735779.9613</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>15558.233</t>
+          <t>17887020934.1309</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>15815.484</t>
+          <t>23040515762.0654</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>16001.517</t>
+          <t>22249486131.7537</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>16349.601</t>
+          <t>23403048257.5645</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>16445.736</t>
+          <t>27117175820.5552</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>16719.945</t>
+          <t>26577433359.7417</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>17008.748</t>
+          <t>34946394881.1323</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>17336.604</t>
+          <t>38564300682.8568</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>17904.524</t>
+          <t>36610322477.2671</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>18312.139</t>
+          <t>31289004710.6036</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>18844.801</t>
+          <t>37239374172.8616</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>19188.989</t>
+          <t>37458111694.5556</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>19242.531</t>
+          <t>39185859235.357</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>19878.819</t>
+          <t>43420399576.302</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>20057.919</t>
+          <t>42182340275.1501</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>20161.636</t>
+          <t>43336278986.7749</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>18217.121</t>
+          <t>37505075438.54</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>16871.245</t>
+          <t>34144518523.1121</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>17130.323</t>
+          <t>35772260863.9875</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>17634.785</t>
+          <t>37407128195.5949</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18370.706</t>
+          <t>33809251038.7631</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>17494.803</t>
+          <t>29002998016.6823</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17205.919</t>
+          <t>32229372326.9175</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>17256.738</t>
+          <t>31790303999.005</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>16754.465</t>
+          <t>-1775.34664520021</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>9597.736</t>
+          <t>1230.20260629081</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>10602.33</t>
+          <t>-4426.69049805632</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>10614.764</t>
+          <t>-11121.59951636</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>11006.706</t>
+          <t>-11306.0824062674</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>11165.384</t>
+          <t>499.208131376352</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>11538.466</t>
+          <t>-46.0781233323702</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>11708.711</t>
+          <t>-12676.9230927786</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>11880.586</t>
+          <t>-17525.377056632</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>12263.125</t>
+          <t>-19551.2403621282</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>12592.446</t>
+          <t>-14531.5122959212</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>13099.361</t>
+          <t>-14015.0413394981</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>13550.895</t>
+          <t>-23947.0628596816</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>14127.637</t>
+          <t>1990.20922413983</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>14445.014</t>
+          <t>-9799.06124486493</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>14471.033</t>
+          <t>12386.5281539102</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>14990.991</t>
+          <t>-3614.34704653433</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>15210.466</t>
+          <t>-20989.3852912774</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>15346.896</t>
+          <t>-6498.62575612698</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>16011.084</t>
+          <t>-21983.5790659011</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>14779.538</t>
+          <t>-33469.5660443102</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>15007.815</t>
+          <t>9176.9858668724</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>15410.976</t>
+          <t>6252.55817980168</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16061.608</t>
+          <t>40581.4252494119</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>15341.586</t>
+          <t>62105.855916508</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15113.767</t>
+          <t>63961.9308259678</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>15151.871</t>
+          <t>65891.8482485847</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>30702.625</t>
+          <t>-29881516565.5065</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>19969.392</t>
+          <t>-10728787322.7794</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>19352.518</t>
+          <t>-12633795621.3284</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>20670.46</t>
+          <t>-13489095370.4504</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>23624.359</t>
+          <t>-17653900360.0258</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>23850.533</t>
+          <t>-16719709786.7381</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>24923.269</t>
+          <t>-17884516352.0555</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>28005.17</t>
+          <t>-20990045446.0048</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>26705.554</t>
+          <t>-21471212274.8582</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>31397.19</t>
+          <t>-28964581877.1656</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>33234.104</t>
+          <t>-31966608411.4412</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>31439.099</t>
+          <t>-30554162356.2153</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>29236.045</t>
+          <t>-26053380521.2377</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>32658.893</t>
+          <t>-30528395832.1719</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>33944.688</t>
+          <t>-31358310892.6865</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>31305.501</t>
+          <t>-33203416052.4923</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>35189.262</t>
+          <t>-36235424370.7966</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>33493.155</t>
+          <t>-36210910694.186</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>33460.248</t>
+          <t>-37045228977.5734</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>27834.007</t>
+          <t>-31548004452.0942</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>24293.441</t>
+          <t>-29377189491.7867</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>23423.956</t>
+          <t>-31064126907.5624</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>24220.136</t>
+          <t>-31703688144.7902</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>25397.772</t>
+          <t>-27309852164.7688</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>23288.566</t>
+          <t>-23291217612.4865</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>24133.817</t>
+          <t>-26091223221.3462</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>24565.549</t>
+          <t>-25995419817.7171</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>102367.813086498</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>116695.604304853</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>127779.41724371</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.152</t>
+          <t>114988.749215978</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>132846.89837218</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>150024.030256838</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.233</t>
+          <t>144823.39066344</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.254</t>
+          <t>148483.037041433</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>156900.85190544</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.258</t>
+          <t>170931.224775202</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.291</t>
+          <t>191369.903518455</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.296</t>
+          <t>204334.827638307</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.284</t>
+          <t>212982.077391914</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.321</t>
+          <t>211980.132524221</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.332</t>
+          <t>212076.977575</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.353</t>
+          <t>284096.276543001</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.413</t>
+          <t>321258.551729909</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.434</t>
+          <t>354835.139454407</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.422</t>
+          <t>330452.069557159</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>319681.450172798</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>0.351</t>
+          <t>320022.679594517</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>0.307</t>
+          <t>337760.547940672</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>358638.975206971</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>351559.548977727</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>346544.681501522</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>353784.865288256</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>361432.848195125</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>10093.519</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>7975.528</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>8046.917</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>8126.6</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>8226.269</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>8225.809</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>8478.735</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>8500.565</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>8557.01</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>8664.831</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>8897.021</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>9097.599</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>9377.484</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>9643.757</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>9956.806</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>10109.002</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>10410.634</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>10508.974</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>10701.015</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>9615.754</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>9025.034</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>8994.09</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>9302.209</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>9776.311</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>9377.672</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>9078.818</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>9197.884</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>169277.54628597</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>207436.239554044</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>238716.834138694</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>206515.586265252</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>247058.797324555</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>265133.124936434</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>265045.627882214</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>272197.275394199</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>287831.954690131</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>312841.713422113</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>350819.780311208</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>374465.180421657</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>405719.153097115</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>402603.061872046</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>407889.477523641</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>534527.555333532</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>606263.381433462</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>655924.890922854</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>627292.139092732</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>608117.499625769</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>617566.146918964</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>642301.961064515</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>678245.691859897</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>662372.520938505</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>659680.563920622</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>676825.633587905</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>689612.772506665</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>11312.783</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>8816.216</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>12036.821</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>9944.37</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>14654.586</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>11730.048</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>11677.21</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>11727.647</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>12050.756</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>16278.247</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>16034.882</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>16221.475</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>13938.726</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>14908.018</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>14890.393</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>16443.074</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>17206.697</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>16758.855</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>17637.848</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>13480.09</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>10924.604</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>14125.461</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>14218.061</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>14084.651</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>13231.108</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>14005.955</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>13631.556</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>48.1</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>8.86</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>-11.92</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>6.74</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>-24.89</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>-4.81</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>-1.19</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>-0.16</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>-1.41</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>-24.67</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>-21.47</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>-19.25</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>-2.78</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>-5.23</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>-2.99</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>-11.99</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>-12.88</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>-9.24</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>-12.99</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>18.78</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>35.29</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>6.25</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>8.39</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>14.04</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>15.95</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>7.91</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>11.15</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>13.969</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>7.621</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>6.239</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>7.803</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>7.462</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>6.532</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>6.617</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>6.943</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>6.874</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>6.281</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>5.925</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>5.454</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>4.373</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>4.918</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>5.36</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>3.782</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>3.662</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>3.134</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>3.36</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>3.715</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>2.855</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>2.699</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>2.795</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>3.037</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>2.808</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>2.838</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>2.788</t>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>142567.242922025</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>150650.65774067</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>163943.762456947</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>157579.884351682</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>171350.585898757</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>196192.040911669</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>186758.701389015</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>208429.803571918</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>227746.190687501</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>257127.763988954</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>288669.361368489</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>305124.003582159</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>348930.439338542</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>350339.755251481</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>351344.278923224</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>490618.934431955</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>555123.4124265</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>634439.096971622</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>586486.961264214</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>541249.705798881</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>553641.485394885</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>591279.998822958</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>629534.591144914</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>625961.243878326</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>626407.644240411</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>637421.286340883</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>659477.917449004</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>16754464624.6072</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>9597736200.00178</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>10602330439.9958</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>10614763639.9956</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>11006706360.002</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>11165384360.0006</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>11538465813.3299</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>11708710519.9993</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>11880585600.0021</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>12263125159.9935</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>12592445839.9989</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>13099361079.9982</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>13550894760.0066</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>14127636639.9992</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>14445014480.0031</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>14471033200.0064</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>14990991080.0003</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>15210465919.9955</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>15346896239.9954</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>16011083787.5824</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>14779537505.3079</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>15007815165.8645</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>15410976371.6252</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>16061608183.5885</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>15341585690.1753</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>15113767078.3664</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>15151870671.1626</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>19097640207.0913</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>14507826320.0021</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>15448211479.9975</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>15558233079.996</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>15815484360.0018</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>16001517480.001</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>16349601493.3311</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>16445735800</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>16719944800.0032</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>17008748119.9935</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>17336604480.0033</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>17904524039.9983</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>18312138520.005</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>18844801039.9999</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>19188989039.9973</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>19242531360.0076</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>19878819479.998</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>20057919439.999</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>20161635519.999</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>18217120938.7482</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>16871244784.4711</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>17130322807.0613</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>17634785256.4646</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>18370706210.7791</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>17494803266.5825</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>17205919147.3279</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>17256737660.0571</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>10093519079.6486</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>7975527515.18724</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>8046916849.35512</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>8126599806.52603</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>8226269430.88191</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>8225808975.36749</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>8478734792.89538</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>8500564820.00583</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>8557010266.91289</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>8664830531.76501</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>8897020980.93651</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>9097598814.29246</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>9377483869.55889</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>9643756759.43332</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>9956806274.45176</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>10109002314.8111</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>10410634025.3356</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>10508973871.5855</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>10701015043.8729</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>9615753697.70684</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>9025033523.08088</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>8994090033.27657</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>9302209219.87773</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>9776310856.31991</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>9377671526.62478</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>9078818492.34775</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>9197883611.33321</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>10572269.327008</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>7763499.99999979</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>8322899.99999864</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>8390300.00000069</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>8571100.00000246</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>8719599.99999941</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>8948100.00000111</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>9081099.99999795</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>9245499.99999836</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>9465100.00000224</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>9623299.99999809</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>9968500.00000006</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>10218300.0000003</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>10512199.9999984</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>10740300.0000016</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>10920599.9999999</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>11214600.0000012</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>11394600.0000016</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>11545599.9999998</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>10416107.6928504</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>9643323.05075511</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>9818890.97615731</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>9986568.22250249</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>10296647.4071664</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>9798823.85416946</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>9613993.49758796</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>9634264.98219542</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>9298208.21915253</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>6498499.99999991</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>7062599.99999862</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>7119700.00000065</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>7319700.00000304</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>7455799.99999858</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>7687800.00000113</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>7832699.99999792</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>7964499.99999884</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>8195500.00000254</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>8354599.99999786</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>8678100.00000006</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>8943500.00000008</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>9251899.99999874</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>9472000.00000179</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>9628799.99999999</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>9889400.00000153</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>10072300.0000012</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>10213199.9999989</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>9208729.17218387</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>8502097.35789649</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>8655096.26435334</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>8770455.79968284</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>9037083.34929747</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>8621242.53227029</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>8467581.1606716</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>8482628.89335786</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>19097640207.0913</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>14507826320.0021</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>15448211479.9975</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>15558233079.996</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>15815484360.0018</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>16001517480.001</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>16349601493.3311</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>16445735800</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>16719944800.0032</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>17008748119.9935</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>17336604480.0033</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>17904524039.9983</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>18312138520.005</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>18844801039.9999</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>19188989039.9973</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>19242531360.0076</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>19878819479.998</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>20057919439.999</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>20161635519.999</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>18217120938.7482</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>16871244784.4711</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>17130322807.0613</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>17634785256.4646</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>18370706210.7791</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>17494803266.5825</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>17205919147.3279</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>17256737660.0571</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>16754464624.6072</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>9597736200.00178</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>10602330439.9958</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>10614763639.9956</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>11006706360.002</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>11165384360.0006</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>11538465813.3299</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>11708710519.9993</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>11880585600.0021</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>12263125159.9935</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>12592445839.9989</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>13099361079.9982</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>13550894760.0066</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>14127636639.9992</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>14445014480.0031</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>14471033200.0064</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>14990991080.0003</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>15210465919.9955</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>15346896239.9954</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>16011083787.5824</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>14779537505.3079</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>15007815165.8645</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>15410976371.6252</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>16061608183.5885</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>15341585690.1753</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>15113767078.3664</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>15151870671.1626</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>642849.110429386</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>735484.990365204</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>830650.841650739</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>737218.495798289</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>867262.486498437</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>971243.02212609</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>940205.341157796</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>996325.106259982</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>1051828.92989796</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>1174263.92698113</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>1319988.0312954</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>1403514.38552445</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>1529832.72507312</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>1537144.38342525</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>1549717.29408319</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>2058210.79941558</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>2333689.00687643</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>2584239.25020315</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>2430072.77168522</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2293102.01838561</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>2348828.7313627</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>2468703.66328835</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2624120.56835423</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>2578406.83718431</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2564235.90609036</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>2587116.75928971</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>2700094.0032167</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>189175.257540555</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>229068.41598323</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>263100.724337554</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>227966.974078219</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>272707.534523982</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>294860.199458775</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>296521.503764644</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>302169.362993172</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>319963.637909036</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>347917.147415736</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>389943.603188172</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>417901.327888781</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>448597.586269142</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>447017.556869721</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>455911.404798483</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>596922.955377341</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>677672.10896567</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>739229.98518753</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>702722.087418966</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>681784.693964548</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>693992.913896224</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>721901.895549783</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>761915.825739058</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>744663.657377709</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>741471.400513113</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>761412.861194616</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>775474.127776046</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
         </is>
       </c>
     </row>
@@ -3614,7 +5855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3637,36 +5878,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3678,331 +5934,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -4039,6 +6659,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
